--- a/results_ablation/FP1_ablation_result.xlsx
+++ b/results_ablation/FP1_ablation_result.xlsx
@@ -54,6 +54,7 @@
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">평균 </t>
     </r>
@@ -88,6 +89,7 @@
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">평균 </t>
     </r>
@@ -114,6 +116,7 @@
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">개선율 </t>
     </r>
@@ -148,6 +151,7 @@
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">평균 </t>
     </r>
@@ -182,6 +186,7 @@
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">평균 </t>
     </r>
@@ -205,6 +210,7 @@
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">차이 </t>
     </r>
@@ -228,6 +234,7 @@
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">개선율 </t>
     </r>
@@ -298,6 +305,7 @@
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">평균 </t>
     </r>
@@ -332,6 +340,7 @@
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">회</t>
     </r>
@@ -366,6 +375,7 @@
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">회</t>
     </r>
@@ -400,6 +410,7 @@
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">회</t>
     </r>
@@ -434,6 +445,7 @@
         <color rgb="FFFFFFFF"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">회</t>
     </r>
@@ -487,6 +499,7 @@
         <sz val="11"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">평균</t>
     </r>
@@ -536,12 +549,14 @@
       <color rgb="FFFFFFFF"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="12"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -555,6 +570,7 @@
       <sz val="11"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -716,7 +732,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="1" style="0" width="25"/>
   </cols>
@@ -825,7 +841,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="18"/>
@@ -986,7 +1002,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="18"/>
@@ -1147,18 +1163,17 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="62.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="60.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="8.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="61.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="41.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="6.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="60.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="5.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="6.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="60.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="60.86"/>
   </cols>
   <sheetData>
@@ -1416,7 +1431,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="18"/>
@@ -1577,7 +1592,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="18"/>
@@ -1738,7 +1753,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="18"/>
@@ -1899,7 +1914,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="18"/>
@@ -2060,7 +2075,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="18"/>
@@ -2221,7 +2236,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="18"/>
@@ -2382,7 +2397,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="18"/>
@@ -2543,7 +2558,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="2" style="0" width="18"/>
